--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_DAMEX CB ALGECIRAS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_DAMEX CB ALGECIRAS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA40"/>
+  <dimension ref="A1:BA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>165.12</v>
+        <v>472.08</v>
       </c>
       <c r="C2" t="n">
-        <v>160.28</v>
+        <v>469.1999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>99.82530571499876</v>
+        <v>105.7118499573743</v>
       </c>
       <c r="E2" t="n">
-        <v>96.70576491140505</v>
+        <v>96.7604433077579</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4625</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="G2" t="n">
-        <v>0.164726553920492</v>
+        <v>0.1586226563056962</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2207792207792208</v>
+        <v>0.3436293436293436</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4083333333333333</v>
+        <v>0.336734693877551</v>
       </c>
       <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="n">
+        <v>49</v>
+      </c>
+      <c r="L2" t="n">
+        <v>62</v>
+      </c>
+      <c r="M2" t="n">
+        <v>36</v>
+      </c>
+      <c r="N2" t="n">
+        <v>70</v>
+      </c>
+      <c r="O2" t="n">
+        <v>144</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3673469387755102</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>21</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.05357142857142857</v>
+      </c>
+      <c r="T2" t="n">
         <v>12</v>
       </c>
-      <c r="K2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>28</v>
-      </c>
-      <c r="M2" t="n">
-        <v>11</v>
-      </c>
-      <c r="N2" t="n">
-        <v>24</v>
-      </c>
-      <c r="O2" t="n">
-        <v>45</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R2" t="n">
-        <v>10</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05</v>
+        <v>0.06377551020408163</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2166666666666667</v>
+        <v>0.2168367346938775</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.275</v>
+        <v>0.2984693877551021</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3764705882352941</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2735042735042735</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.066666666666667</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.96</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9661016949152542</v>
+        <v>0.9504950495049505</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.625</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.550561797752809</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.647058823529412</v>
+        <v>1.878787878787879</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6</v>
+        <v>0.8539325842696629</v>
       </c>
       <c r="AO2" t="n">
-        <v>4</v>
+        <v>4.404494382022472</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.6</v>
+        <v>5.258426966292135</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>82.56</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>80.13999999999999</v>
+        <v>78.19999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>99.82530571499876</v>
+        <v>105.7118499573743</v>
       </c>
       <c r="E3" t="n">
-        <v>96.70576491140505</v>
+        <v>96.76044330775791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4625</v>
+        <v>0.4642857142857144</v>
       </c>
       <c r="G3" t="n">
-        <v>0.164726553920492</v>
+        <v>0.1586226563056962</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2207792207792208</v>
+        <v>0.3436293436293437</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4083333333333333</v>
+        <v>0.3367346938775511</v>
       </c>
       <c r="J3" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.166666666666666</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10.33333333333333</v>
+      </c>
+      <c r="M3" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>14</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5.5</v>
-      </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
-        <v>0.375</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.05357142857142858</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05</v>
+        <v>0.06377551020408165</v>
       </c>
       <c r="W3" t="n">
-        <v>4</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2166666666666667</v>
+        <v>0.2168367346938776</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.5</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="AA3" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.275</v>
+        <v>0.2984693877551021</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3764705882352941</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2735042735042735</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.066666666666667</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.96</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9661016949152542</v>
+        <v>0.9504950495049506</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.625</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.5505617977528089</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.647058823529412</v>
+        <v>1.878787878787879</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6</v>
+        <v>0.8539325842696629</v>
       </c>
       <c r="AO3" t="n">
-        <v>4</v>
+        <v>4.404494382022471</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>5.258426966292134</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>155.44</v>
+        <v>466.32</v>
       </c>
       <c r="C4" t="n">
-        <v>160.28</v>
+        <v>469.1999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>96.70576491140505</v>
+        <v>96.7604433077579</v>
       </c>
       <c r="E4" t="n">
-        <v>99.82530571499876</v>
+        <v>105.7118499573743</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4352517985611511</v>
+        <v>0.4220930232558139</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1432816811717257</v>
+        <v>0.1385713295919075</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3707865168539326</v>
+        <v>0.3814432989690721</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2446043165467626</v>
+        <v>0.2116279069767442</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="O4" t="n">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4748201438848921</v>
+        <v>0.4232558139534884</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07913669064748201</v>
+        <v>0.08837209302325581</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06474820143884892</v>
+        <v>0.06976744186046512</v>
       </c>
       <c r="W4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1654676258992806</v>
+        <v>0.1674418604651163</v>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2158273381294964</v>
+        <v>0.2511627906976744</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.456043956043956</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9120879120879121</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.5842696629213483</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.3873873873873874</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.166666666666667</v>
+        <v>1.723404255319149</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.074074074074074</v>
+        <v>1.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.148148148148148</v>
+        <v>5.375</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.222222222222222</v>
+        <v>6.625</v>
       </c>
     </row>
     <row r="5">
@@ -1040,124 +1040,124 @@
         <v>77.72</v>
       </c>
       <c r="C5" t="n">
-        <v>80.13999999999999</v>
+        <v>78.19999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>96.70576491140505</v>
+        <v>96.76044330775791</v>
       </c>
       <c r="E5" t="n">
-        <v>99.82530571499876</v>
+        <v>105.7118499573743</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4352517985611511</v>
+        <v>0.422093023255814</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1432816811717257</v>
+        <v>0.1385713295919075</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3707865168539326</v>
+        <v>0.3814432989690721</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2446043165467626</v>
+        <v>0.2116279069767442</v>
       </c>
       <c r="J5" t="n">
-        <v>11.5</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>7.5</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="O5" t="n">
-        <v>33</v>
+        <v>30.33333333333333</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4748201438848921</v>
+        <v>0.4232558139534884</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>5.5</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07913669064748201</v>
+        <v>0.08837209302325583</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="U5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06474820143884892</v>
+        <v>0.06976744186046513</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1654676258992806</v>
+        <v>0.1674418604651163</v>
       </c>
       <c r="Z5" t="n">
         <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2158273381294964</v>
+        <v>0.2511627906976744</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.4560439560439561</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.3055555555555555</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9120879120879122</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.5842696629213483</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.3873873873873874</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.166666666666667</v>
+        <v>1.723404255319149</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.074074074074074</v>
+        <v>1.25</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.148148148148148</v>
+        <v>5.374999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.222222222222222</v>
+        <v>6.624999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1429,41 +1429,41 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
+        <v>17</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
         <v>7</v>
       </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1471,19 +1471,19 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1544,47 +1544,47 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>26:23</t>
+          <t>73:00</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>5</v>
+        <v>11.88</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.5</v>
+        <v>0.167</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.5</v>
+        <v>0.218</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.4</v>
+        <v>0.253</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.6</v>
+        <v>0.421</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.667</v>
+        <v>1.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.333</v>
+        <v>2.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.083</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.039</v>
+        <v>0.104</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.238</v>
+        <v>0.196</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.044</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="9">
@@ -1594,162 +1594,162 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>53</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>22</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>28</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="n">
         <v>2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>21</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="U9" t="n">
         <v>5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W9" t="n">
+        <v>12</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>134:30</t>
+        </is>
+      </c>
+      <c r="AO9" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AV9" t="n">
         <v>4</v>
       </c>
-      <c r="Z9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>42:06</t>
-        </is>
-      </c>
-      <c r="AO9" t="n">
-        <v>22.64</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.667</v>
-      </c>
       <c r="AW9" t="n">
-        <v>6.333</v>
+        <v>4.909</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.236</v>
+        <v>0.194</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.099</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.192</v>
+        <v>0.175</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.051</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="10">
@@ -1759,82 +1759,82 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>64</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
-        <v>13</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>17</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>38</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>7</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1849,72 +1849,72 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>0.533</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AL10" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.333</v>
+        <v>0.368</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>34:05</t>
+          <t>118:34</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>8.76</v>
+        <v>52.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.643</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.742</v>
+        <v>0.62</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.484</v>
+        <v>1.217</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.571</v>
+        <v>0.289</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.113</v>
+        <v>0.194</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.053</v>
+        <v>0.057</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="11">
@@ -1924,35 +1924,35 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:36</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -2089,67 +2089,67 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="R12" t="n">
+        <v>25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
         <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>3</v>
@@ -2158,19 +2158,19 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2185,66 +2185,66 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AK12" t="n">
         <v>1</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AM12" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>118:38</t>
+        </is>
+      </c>
+      <c r="AO12" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="AT12" t="n">
         <v>0.25</v>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>42:14</t>
-        </is>
-      </c>
-      <c r="AO12" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AU12" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.667</v>
+        <v>3.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.146</v>
+        <v>0.149</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.049</v>
+        <v>0.064</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.106</v>
+        <v>0.149</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="13">
@@ -2254,162 +2254,162 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>55</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23</v>
+      </c>
+      <c r="I13" t="n">
+        <v>37</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>26</v>
+      </c>
+      <c r="U13" t="n">
+        <v>11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" t="n">
-        <v>17</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>42:36</t>
+          <t>140:03</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>25.48</v>
+        <v>72.28</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.167</v>
+        <v>0.39</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.334</v>
+        <v>0.48</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.51</v>
+        <v>0.761</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.235</v>
+        <v>0.208</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.75</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.833</v>
+        <v>1.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>2</v>
+        <v>2.733</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.833</v>
+        <v>3.933</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.263</v>
+        <v>0.225</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.098</v>
+        <v>0.074</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.127</v>
+        <v>0.09</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.114</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="14">
@@ -2419,162 +2419,162 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="D14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" t="n">
+        <v>35</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>53</v>
+      </c>
+      <c r="H14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" t="n">
+        <v>28</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K14" t="n">
+        <v>14</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>55</v>
+      </c>
+      <c r="U14" t="n">
         <v>6</v>
       </c>
-      <c r="E14" t="n">
-        <v>13</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="V14" t="n">
+        <v>10</v>
+      </c>
+      <c r="W14" t="n">
+        <v>8</v>
+      </c>
+      <c r="X14" t="n">
         <v>5</v>
       </c>
-      <c r="G14" t="n">
-        <v>16</v>
-      </c>
-      <c r="H14" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>16</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2</v>
-      </c>
       <c r="Y14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AB14" t="n">
         <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="AH14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.6</v>
+        <v>0.412</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.182</v>
+        <v>0.222</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>56:46</t>
+          <t>165:33</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>35.08</v>
+        <v>114.32</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.466</v>
+        <v>0.46</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.514</v>
+        <v>0.513</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.901</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.207</v>
+        <v>0.25</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.667</v>
+        <v>1.143</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.667</v>
+        <v>6.286</v>
       </c>
       <c r="AW14" t="n">
-        <v>10.333</v>
+        <v>7.429</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.271</v>
+        <v>0.302</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.063</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.057</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="15">
@@ -2584,101 +2584,101 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>86</v>
+      </c>
+      <c r="D15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" t="n">
+        <v>51</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" t="n">
+        <v>45</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>40</v>
+      </c>
+      <c r="L15" t="n">
+        <v>21</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>10</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>99</v>
+      </c>
+      <c r="U15" t="n">
+        <v>9</v>
+      </c>
+      <c r="V15" t="n">
+        <v>18</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" t="n">
-        <v>23</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>13</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>9</v>
-      </c>
-      <c r="I15" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>13</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="Y15" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE15" t="n">
         <v>3</v>
       </c>
-      <c r="W15" t="n">
-        <v>2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AF15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG15" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
@@ -2699,47 +2699,47 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>48:36</t>
+          <t>154:26</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>21.6</v>
+        <v>77.8</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.538</v>
+        <v>0.549</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.587</v>
+        <v>0.607</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.065</v>
+        <v>1.105</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.093</v>
+        <v>0.09</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.5</v>
+        <v>7.286</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.5</v>
+        <v>7.429</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.195</v>
+        <v>0.22</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.043</v>
+        <v>0.129</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.24</v>
+        <v>0.218</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="16">
@@ -2749,162 +2749,162 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>27</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="C16" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5</v>
+      </c>
+      <c r="X16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="n">
-        <v>8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="Y16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="AC16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2</v>
       </c>
-      <c r="X16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
       <c r="AI16" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>33:56</t>
+          <t>121:24</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>16.2</v>
+        <v>52.84</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.375</v>
+        <v>0.366</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.458</v>
+        <v>0.436</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.802</v>
+        <v>0.757</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.123</v>
+        <v>0.132</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.333</v>
+        <v>0.244</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="AV16" t="n">
-        <v>6</v>
+        <v>5.857</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>6.714</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="17">
@@ -2914,82 +2914,82 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>64</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>29</v>
+      </c>
+      <c r="H17" t="n">
+        <v>19</v>
+      </c>
+      <c r="I17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J17" t="n">
+        <v>13</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>18</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>35</v>
+      </c>
+      <c r="U17" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="W17" t="n">
+        <v>13</v>
+      </c>
+      <c r="X17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y17" t="n">
         <v>9</v>
       </c>
-      <c r="F17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G17" t="n">
-        <v>11</v>
-      </c>
-      <c r="H17" t="n">
-        <v>9</v>
-      </c>
-      <c r="I17" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>8</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>18</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>8</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>7</v>
-      </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.875</v>
+        <v>0.643</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3010,66 +3010,66 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AK17" t="n">
         <v>4</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>3</v>
-      </c>
       <c r="AL17" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.429</v>
+        <v>0.222</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>70:10</t>
+          <t>169:58</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>33.28</v>
+        <v>71.12</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.65</v>
+        <v>0.511</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.591</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.052</v>
+        <v>0.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.24</v>
+        <v>0.239</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.45</v>
+        <v>0.432</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.5</v>
+        <v>2.588</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.25</v>
+        <v>3.353</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.208</v>
+        <v>0.183</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.026</v>
+        <v>0.05</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.171</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="18">
@@ -3079,37 +3079,37 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -3127,41 +3127,41 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
+        <v>9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
@@ -3175,13 +3175,13 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3194,20 +3194,20 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>03:08</t>
+          <t>25:29</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -3225,13 +3225,13 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -3570,11 +3570,11 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#50 K. VAN BRANDWIJK</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -3601,10 +3601,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:49</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
@@ -3735,163 +3735,163 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>18</v>
       </c>
-      <c r="K22" t="n">
-        <v>56</v>
-      </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.533</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>400:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>182.12</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.879</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.408</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3900,163 +3900,163 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>155</v>
+        <v>496</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="E23" t="n">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="G23" t="n">
-        <v>53</v>
+        <v>202</v>
       </c>
       <c r="H23" t="n">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="I23" t="n">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="J23" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="K23" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="L23" t="n">
+        <v>89</v>
+      </c>
+      <c r="M23" t="n">
+        <v>46</v>
+      </c>
+      <c r="N23" t="n">
+        <v>12</v>
+      </c>
+      <c r="O23" t="n">
+        <v>16</v>
+      </c>
+      <c r="P23" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>36</v>
+      </c>
+      <c r="R23" t="n">
+        <v>145</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>327</v>
+      </c>
+      <c r="U23" t="n">
+        <v>50</v>
+      </c>
+      <c r="V23" t="n">
+        <v>49</v>
+      </c>
+      <c r="W23" t="n">
+        <v>62</v>
+      </c>
+      <c r="X23" t="n">
         <v>33</v>
       </c>
-      <c r="M23" t="n">
-        <v>19</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>11</v>
-      </c>
-      <c r="R23" t="n">
-        <v>51</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>111</v>
-      </c>
-      <c r="U23" t="n">
-        <v>23</v>
-      </c>
-      <c r="V23" t="n">
-        <v>15</v>
-      </c>
-      <c r="W23" t="n">
-        <v>26</v>
-      </c>
-      <c r="X23" t="n">
-        <v>12</v>
-      </c>
       <c r="Y23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Z23" t="n">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.485</v>
+        <v>0.486</v>
       </c>
       <c r="AB23" t="n">
         <v>4</v>
       </c>
       <c r="AC23" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.364</v>
+        <v>0.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AF23" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.222</v>
+        <v>0.48</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="AI23" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.261</v>
+        <v>0.376</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AL23" t="n">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.3</v>
+        <v>0.274</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>400:00</t>
+          <t>1225:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>188.44</v>
+        <v>561.08</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.435</v>
+        <v>0.464</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.48</v>
+        <v>0.525</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.823</v>
+        <v>0.884</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.143</v>
+        <v>0.159</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.245</v>
+        <v>0.337</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.074</v>
+        <v>0.854</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.148</v>
+        <v>4.404</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.222</v>
+        <v>5.258</v>
       </c>
       <c r="AX23" t="n">
         <v>0.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.156</v>
+        <v>0.124</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4065,598 +4065,598 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
+          <t>Rival</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>454</v>
+      </c>
+      <c r="D24" t="n">
+        <v>108</v>
+      </c>
+      <c r="E24" t="n">
+        <v>250</v>
+      </c>
+      <c r="F24" t="n">
+        <v>49</v>
+      </c>
+      <c r="G24" t="n">
+        <v>180</v>
+      </c>
+      <c r="H24" t="n">
+        <v>91</v>
+      </c>
+      <c r="I24" t="n">
+        <v>153</v>
+      </c>
+      <c r="J24" t="n">
+        <v>100</v>
+      </c>
+      <c r="K24" t="n">
+        <v>170</v>
+      </c>
+      <c r="L24" t="n">
+        <v>111</v>
+      </c>
+      <c r="M24" t="n">
+        <v>53</v>
+      </c>
+      <c r="N24" t="n">
+        <v>16</v>
+      </c>
+      <c r="O24" t="n">
+        <v>12</v>
+      </c>
+      <c r="P24" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>34</v>
+      </c>
+      <c r="R24" t="n">
+        <v>147</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>300</v>
+      </c>
+      <c r="U24" t="n">
+        <v>52</v>
+      </c>
+      <c r="V24" t="n">
+        <v>43</v>
+      </c>
+      <c r="W24" t="n">
+        <v>81</v>
+      </c>
+      <c r="X24" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>182</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>72</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>108</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>1225:00</t>
+        </is>
+      </c>
+      <c r="AO24" t="n">
+        <v>577.3200000000001</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>6.625</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#3 R. SANCHES CARDOSO MENDES (Per Game)</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>13</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0.044</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#4 M. HETOR MENSAH (Per Game)</t>
+          <t>#3 R. SANCHES CARDOSO MENDES (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0.167</v>
       </c>
       <c r="E26" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0.167</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0.333</v>
       </c>
       <c r="J26" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>19</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AO26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AU26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>15</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>21:03</t>
-        </is>
-      </c>
-      <c r="AO26" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0.667</v>
-      </c>
       <c r="AV26" t="n">
-        <v>5.667</v>
+        <v>1.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.333</v>
+        <v>2.2</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.236</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.099</v>
+        <v>0.104</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.192</v>
+        <v>0.196</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.051</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#7 A. ARTILES AGUILAR (Per Game)</t>
+          <t>#4 M. HETOR MENSAH (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8.833</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="C27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="M27" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="F27" t="n">
+      <c r="P27" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>53</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="W27" t="n">
         <v>2</v>
       </c>
-      <c r="I27" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="X27" t="n">
-        <v>1.5</v>
+        <v>0.833</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="Z27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG27" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>1.833</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>0.455</v>
       </c>
       <c r="AK27" t="n">
         <v>0.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.5</v>
+        <v>1.833</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>4.38</v>
+        <v>9.973000000000001</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.643</v>
+        <v>0.523</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.742</v>
+        <v>0.543</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.484</v>
+        <v>0.886</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.571</v>
+        <v>0.159</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>4.909</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.113</v>
+        <v>0.194</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.053</v>
+        <v>0.175</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#8 A. MONTENEGRO MOYA (Per Game)</t>
+          <t>#7 A. ARTILES AGUILAR (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4665,46 +4665,46 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4713,137 +4713,137 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>3.167</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>8.766999999999999</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.217</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#9 A. DIAZ ROLLANO (Per Game)</t>
+          <t>#8 A. MONTENEGRO MOYA (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
         <v>1</v>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>-6</v>
-      </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
@@ -4851,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -4878,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -4887,931 +4887,931 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>00:31</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.497</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.106</v>
+        <v>0.324</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#10 B. EDOKPAYI MANCERA (Per Game)</t>
+          <t>#9 A. DIAZ ROLLANO (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>6.5</v>
+        <v>4.167</v>
       </c>
       <c r="D30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="n">
-        <v>4</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>-4</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>6.733</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AV30" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA30" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>21:18</t>
-        </is>
-      </c>
-      <c r="AO30" t="n">
-        <v>12.74</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2</v>
-      </c>
       <c r="AW30" t="n">
-        <v>2.833</v>
+        <v>3.75</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.263</v>
+        <v>0.149</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.098</v>
+        <v>0.064</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.127</v>
+        <v>0.149</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.114</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#11 R. REID (Per Game)</t>
+          <t>#10 B. EDOKPAYI MANCERA (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9.167</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6.167</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>26</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL31" t="n">
         <v>2</v>
       </c>
-      <c r="C31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="D31" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G31" t="n">
-        <v>8</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>16</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AM31" t="n">
-        <v>0.182</v>
+        <v>0.25</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>28:23</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>17.54</v>
+        <v>12.047</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.466</v>
+        <v>0.39</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.514</v>
+        <v>0.48</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.761</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.207</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.667</v>
+        <v>1.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.667</v>
+        <v>2.733</v>
       </c>
       <c r="AW31" t="n">
-        <v>10.333</v>
+        <v>3.933</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.271</v>
+        <v>0.225</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.063</v>
+        <v>0.09</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.057</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#14 D. ILINCIC (Per Game)</t>
+          <t>#11 R. REID (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>11.5</v>
+        <v>17.167</v>
       </c>
       <c r="D32" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>6.5</v>
+        <v>5.833</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>8.833</v>
       </c>
       <c r="H32" t="n">
-        <v>4.5</v>
+        <v>3.667</v>
       </c>
       <c r="I32" t="n">
-        <v>7.5</v>
+        <v>4.667</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="K32" t="n">
-        <v>6.5</v>
+        <v>2.333</v>
       </c>
       <c r="L32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>55</v>
+      </c>
+      <c r="U32" t="n">
         <v>1</v>
       </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>25</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="X32" t="n">
-        <v>0.5</v>
+        <v>0.833</v>
       </c>
       <c r="Y32" t="n">
-        <v>3</v>
+        <v>1.333</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>2.833</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.6</v>
+        <v>0.471</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.5</v>
+        <v>0.833</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.5</v>
+        <v>1.333</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>2.167</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.5</v>
+        <v>0.615</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>24:18</t>
+          <t>27:35</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>10.8</v>
+        <v>19.053</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.538</v>
+        <v>0.46</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.587</v>
+        <v>0.513</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.065</v>
+        <v>0.901</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.093</v>
+        <v>0.122</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.143</v>
       </c>
       <c r="AV32" t="n">
-        <v>6.5</v>
+        <v>6.286</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.5</v>
+        <v>7.429</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.195</v>
+        <v>0.302</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.043</v>
+        <v>0.006</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.24</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#21 E. EGEA SOLER (Per Game)</t>
+          <t>#14 D. ILINCIC (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>6.5</v>
+        <v>14.333</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>4.667</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="K33" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="O33" t="n">
+        <v>5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>99</v>
+      </c>
+      <c r="U33" t="n">
         <v>1.5</v>
       </c>
-      <c r="G33" t="n">
+      <c r="V33" t="n">
+        <v>3</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Y33" t="n">
         <v>4</v>
       </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="Z33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE33" t="n">
         <v>0.5</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>25:44</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>8.1</v>
+        <v>12.967</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.375</v>
+        <v>0.549</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.458</v>
+        <v>0.607</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.802</v>
+        <v>1.105</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.123</v>
+        <v>0.09</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.333</v>
+        <v>0.588</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AV33" t="n">
-        <v>6</v>
+        <v>7.286</v>
       </c>
       <c r="AW33" t="n">
-        <v>6</v>
+        <v>7.429</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#22 B. GARCIA ALVAREZ (Per Game)</t>
+          <t>#21 E. EGEA SOLER (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>17.5</v>
+        <v>6.667</v>
       </c>
       <c r="D34" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="E34" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G34" t="n">
         <v>4.5</v>
       </c>
-      <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5.5</v>
-      </c>
       <c r="H34" t="n">
-        <v>4.5</v>
+        <v>1.667</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>1.833</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="M34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.5</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>4</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>18</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>4</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4</v>
-      </c>
       <c r="AA34" t="n">
-        <v>0.875</v>
+        <v>0.222</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AC34" t="n">
         <v>0.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM34" t="n">
         <v>0.5</v>
       </c>
-      <c r="AI34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.429</v>
-      </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>35:05</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>16.64</v>
+        <v>8.807</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.65</v>
+        <v>0.366</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.436</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.052</v>
+        <v>0.757</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.24</v>
+        <v>0.132</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.45</v>
+        <v>0.244</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.75</v>
+        <v>0.857</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.5</v>
+        <v>5.857</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.25</v>
+        <v>6.714</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.208</v>
+        <v>0.19</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.026</v>
+        <v>0.042</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.171</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#30 L. PAÑOS HUERTAS (Per Game)</t>
+          <t>#22 B. GARCIA ALVAREZ (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>10.667</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>4.833</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>3.167</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3.833</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5820,46 +5820,46 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>-1</v>
+        <v>35</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5874,179 +5874,179 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>01:34</t>
+          <t>28:19</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>11.853</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.588</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>3.353</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#35 R. HIDALGO SALAZAR (Per Game)</t>
+          <t>#30 L. PAÑOS HUERTAS (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
       <c r="AK36" t="n">
         <v>0</v>
       </c>
@@ -6058,20 +6058,20 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:14</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS36" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="BA36" t="n">
         <v>0</v>
@@ -6104,7 +6104,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#40 R. CALDERON QUIÑONES (Per Game)</t>
+          <t>#35 R. HIDALGO SALAZAR (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6269,11 +6269,11 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#40 R. CALDERON QUIÑONES (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -6300,10 +6300,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -6434,163 +6434,163 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>TOTAL (Per Game)</t>
+          <t>#50 K. VAN BRANDWIJK (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>29.5</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>8.5</v>
+        <v>0.25</v>
       </c>
       <c r="M39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
         <v>1</v>
       </c>
-      <c r="O39" t="n">
-        <v>5</v>
-      </c>
-      <c r="P39" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>79</v>
-      </c>
       <c r="U39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.533</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>200:00</t>
+          <t>00:12</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>91.06</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.879</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.408</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.044</v>
+        <v>1.158</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
         <v>0</v>
@@ -6599,165 +6599,495 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
+          <t>Equip (Per Game)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (Per Game)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>82.667</v>
+      </c>
+      <c r="D41" t="n">
+        <v>14.333</v>
+      </c>
+      <c r="E41" t="n">
+        <v>31.667</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="G41" t="n">
+        <v>33.667</v>
+      </c>
+      <c r="H41" t="n">
+        <v>22</v>
+      </c>
+      <c r="I41" t="n">
+        <v>30.333</v>
+      </c>
+      <c r="J41" t="n">
+        <v>12.667</v>
+      </c>
+      <c r="K41" t="n">
+        <v>30</v>
+      </c>
+      <c r="L41" t="n">
+        <v>14.833</v>
+      </c>
+      <c r="M41" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>16</v>
+      </c>
+      <c r="P41" t="n">
+        <v>14.833</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6</v>
+      </c>
+      <c r="R41" t="n">
+        <v>24.167</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>327</v>
+      </c>
+      <c r="U41" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="V41" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="W41" t="n">
+        <v>10.333</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>11.667</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>14.167</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>204:10</t>
+        </is>
+      </c>
+      <c r="AO41" t="n">
+        <v>93.51300000000001</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>4.404</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>5.258</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
           <t>Rival (Per Game)</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>75.667</v>
+      </c>
+      <c r="D42" t="n">
+        <v>18</v>
+      </c>
+      <c r="E42" t="n">
+        <v>41.667</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="G42" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" t="n">
+        <v>15.167</v>
+      </c>
+      <c r="I42" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>16.667</v>
+      </c>
+      <c r="K42" t="n">
+        <v>28.333</v>
+      </c>
+      <c r="L42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>8.833</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="O42" t="n">
+        <v>12</v>
+      </c>
+      <c r="P42" t="n">
+        <v>13.333</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="R42" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>300</v>
+      </c>
+      <c r="U42" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7.167</v>
+      </c>
+      <c r="W42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>7.833</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>13.833</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>30.333</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AB42" t="n">
         <v>2</v>
       </c>
-      <c r="C40" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="D40" t="n">
-        <v>19</v>
-      </c>
-      <c r="E40" t="n">
-        <v>43</v>
-      </c>
-      <c r="F40" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G40" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>17</v>
-      </c>
-      <c r="I40" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>30</v>
-      </c>
-      <c r="L40" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2</v>
-      </c>
-      <c r="P40" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>111</v>
-      </c>
-      <c r="U40" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>13</v>
-      </c>
-      <c r="X40" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>33</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF40" t="n">
+      <c r="AC42" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AK42" t="n">
         <v>4.5</v>
       </c>
-      <c r="AG40" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO40" t="n">
-        <v>94.22</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1.074</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>5.148</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>6.222</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="AY40" t="n">
+      <c r="AL42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>204:10</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>96.22</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>6.625</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="AY42" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="AZ40" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="BA40" t="n">
+      <c r="AZ42" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="BA42" t="n">
         <v>0</v>
       </c>
     </row>
